--- a/AtchisonRegime/Outputs/Euro/MSCI_France/df_regTrendSummaryMSCI_France.xlsx
+++ b/AtchisonRegime/Outputs/Euro/MSCI_France/df_regTrendSummaryMSCI_France.xlsx
@@ -1198,13 +1198,13 @@
         <v>45260</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="E35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2160329942437837</v>
+        <v>0.2126154907406677</v>
       </c>
     </row>
   </sheetData>
